--- a/DataTables/DetailText/剧情/011药材有问题.xlsx
+++ b/DataTables/DetailText/剧情/011药材有问题.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70DF6A1-F1D6-4E7D-B9D9-5B6B2AB37E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FBD6C8-1F9F-4BFD-A900-D0482AFF6D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -453,7 +442,29 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>民早我就去衙门讨个说法。</t>
+    <r>
+      <t>明早我就去衙门</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>问问，看看是不是弄错了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -461,11 +472,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -479,7 +490,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -500,7 +511,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -524,6 +535,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -642,7 +660,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -921,27 +939,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -991,7 +1009,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="18.75">
       <c r="A2" s="5" t="s">
         <v>30</v>
       </c>
@@ -1027,65 +1045,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="14"/>
       <c r="L3" s="18"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8" ht="18.75">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -1097,20 +1115,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="93.125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="93.1328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1136,7 +1154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1158,7 +1176,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1180,7 +1198,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1200,7 +1218,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1220,7 +1238,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1240,7 +1258,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1260,7 +1278,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1280,7 +1298,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1290,7 +1308,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1300,7 +1318,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1310,7 +1328,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
